--- a/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
@@ -438,9 +438,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,9 +460,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -493,9 +489,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -503,9 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -513,9 +505,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -548,31 +538,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -589,8 +579,6 @@
           <t>M inhabitant</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>INSEE data</t>
@@ -608,8 +596,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Logistic</t>
@@ -627,8 +613,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -646,8 +630,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -665,8 +647,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -684,8 +664,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -703,8 +681,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -714,7 +690,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net import of vegetal pdcts</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -722,66 +698,75 @@
           <t>ktN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend. Used as a goal but may be adjusted according to territory situation</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>ktN</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>LU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Synth N fertilizer application to cropland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kgN/ha/yr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>kgN/ha/yr</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
@@ -1071,7 +1056,6 @@
       <c r="E12" t="n">
         <v>281</v>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1091,7 +1075,6 @@
       <c r="E13" t="n">
         <v>75</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1155,7 +1138,6 @@
       <c r="E16" t="n">
         <v>45</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1175,7 +1157,6 @@
       <c r="E17" t="n">
         <v>60</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1601,7 +1582,6 @@
           <t xml:space="preserve">Natural meadow </t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="b">
         <v>0</v>
       </c>
@@ -1626,31 +1606,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -1662,11 +1642,9 @@
           <t>Weight diet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1679,11 +1657,9 @@
           <t>Weight synthetic fertilizer use</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1693,14 +1669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weight import/export balance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Weight import</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1710,26 +1684,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1737,8 +1707,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1748,7 +1716,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1756,8 +1724,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1767,7 +1733,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1775,8 +1741,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1786,26 +1750,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1813,8 +1775,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1824,7 +1784,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1832,8 +1792,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1843,7 +1801,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1851,8 +1809,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1862,7 +1818,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1870,8 +1826,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1881,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1889,8 +1843,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1900,26 +1852,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1927,8 +1877,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1938,7 +1886,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1946,8 +1894,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1957,7 +1903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1965,8 +1911,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1976,7 +1920,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1984,8 +1928,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1995,7 +1937,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2003,8 +1945,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2014,7 +1954,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2022,8 +1962,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2033,7 +1971,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2041,8 +1979,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2052,7 +1988,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2060,8 +1996,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2071,7 +2005,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2079,8 +2013,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2090,7 +2022,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2098,8 +2030,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2109,7 +2039,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2117,8 +2047,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2128,7 +2056,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2136,8 +2064,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2147,7 +2073,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2155,8 +2081,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2166,7 +2090,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2174,8 +2098,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2185,7 +2107,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2193,8 +2115,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2204,7 +2124,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2212,8 +2132,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2223,7 +2141,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2231,8 +2149,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2242,7 +2158,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2250,8 +2166,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2261,7 +2175,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2269,8 +2183,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2280,7 +2192,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2288,8 +2200,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2299,7 +2209,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2307,8 +2217,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2318,7 +2226,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2326,8 +2234,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2337,7 +2243,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2345,8 +2251,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2356,16 +2260,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2375,7 +2277,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2383,8 +2285,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2394,7 +2294,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2402,8 +2302,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2413,7 +2311,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2421,8 +2319,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2432,7 +2328,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2440,8 +2336,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2451,7 +2345,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2459,8 +2353,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2470,26 +2362,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2497,8 +2387,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2508,7 +2396,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2516,8 +2404,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2527,7 +2413,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2535,8 +2421,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2546,7 +2430,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2554,8 +2438,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2565,7 +2447,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2573,8 +2455,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2584,16 +2464,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2603,7 +2481,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2611,8 +2489,6 @@
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2622,7 +2498,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2630,8 +2506,6 @@
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2641,17 +2515,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
@@ -438,6 +438,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -459,6 +460,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -487,6 +489,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -494,6 +497,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -501,6 +505,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -533,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,23 +769,6 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methanisation</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1655,7 +1643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1711,37 +1699,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Weight export</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in urban area</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Weight energy</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in rural area</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1758,7 +1750,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1775,41 +1767,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1826,7 +1818,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1860,7 +1852,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1877,41 +1869,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1928,7 +1920,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1945,7 +1937,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1962,7 +1954,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1979,7 +1971,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1996,7 +1988,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2013,7 +2005,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2030,7 +2022,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2047,7 +2039,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2064,7 +2056,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2081,7 +2073,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2098,7 +2090,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2115,7 +2107,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2132,7 +2124,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2149,7 +2141,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2166,7 +2158,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2183,7 +2175,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2200,7 +2192,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2217,7 +2209,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2234,7 +2226,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2251,7 +2243,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2268,7 +2260,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2285,12 +2277,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2302,12 +2294,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2319,7 +2311,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2336,7 +2328,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2353,7 +2345,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2370,7 +2362,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2387,41 +2379,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2438,7 +2430,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2455,7 +2447,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2472,7 +2464,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2489,12 +2481,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2506,12 +2498,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2523,7 +2515,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2540,7 +2532,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2549,40 +2541,6 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Caprines dairy productivity</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Poultry dairy productivity</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
@@ -438,7 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -460,7 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -489,7 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -497,7 +494,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -505,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -538,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +764,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,7 +1655,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1699,41 +1711,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1750,7 +1758,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1767,41 +1775,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1818,7 +1826,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1835,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1852,7 +1860,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1869,41 +1877,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1920,7 +1928,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1937,7 +1945,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1954,7 +1962,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1971,7 +1979,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,7 +1996,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2005,7 +2013,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2022,7 +2030,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,7 +2047,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2056,7 +2064,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2073,7 +2081,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2090,7 +2098,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2107,7 +2115,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2124,7 +2132,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2141,7 +2149,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2158,7 +2166,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2175,7 +2183,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2192,7 +2200,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2209,7 +2217,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2226,7 +2234,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2243,7 +2251,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2260,7 +2268,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2277,12 +2285,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2294,12 +2302,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2311,7 +2319,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2328,7 +2336,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2345,7 +2353,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2362,7 +2370,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2379,41 +2387,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2430,7 +2438,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2447,7 +2455,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2464,7 +2472,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2481,12 +2489,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2498,12 +2506,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2515,7 +2523,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2532,15 +2540,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
@@ -438,7 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -460,7 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -489,7 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -497,7 +494,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -505,7 +501,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -538,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +764,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,7 +1655,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1699,24 +1711,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1733,7 +1743,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1750,7 +1760,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1767,24 +1777,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1801,7 +1811,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1818,7 +1828,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1835,7 +1845,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1852,7 +1862,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1869,24 +1879,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1903,7 +1913,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1920,7 +1930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1937,7 +1947,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1954,7 +1964,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1971,7 +1981,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,7 +1998,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2005,7 +2015,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2022,7 +2032,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,7 +2049,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2056,7 +2066,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2073,7 +2083,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2090,7 +2100,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2107,7 +2117,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2124,7 +2134,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2141,7 +2151,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2158,7 +2168,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2175,7 +2185,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2192,7 +2202,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2209,7 +2219,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2226,7 +2236,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2243,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2260,7 +2270,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2277,12 +2287,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2294,7 +2304,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2311,7 +2321,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2328,7 +2338,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2345,7 +2355,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2362,7 +2372,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2379,24 +2389,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2413,7 +2423,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2430,7 +2440,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2447,7 +2457,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2464,7 +2474,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2481,12 +2491,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2498,7 +2508,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2515,7 +2525,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2532,15 +2542,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
@@ -1618,7 +1618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,24 +1726,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1760,7 +1758,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1777,7 +1775,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1794,24 +1792,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1828,7 +1826,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1845,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1862,7 +1860,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1879,7 +1877,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1896,24 +1894,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1930,7 +1928,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1947,7 +1945,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1964,7 +1962,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1981,7 +1979,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1998,7 +1996,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2015,7 +2013,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2032,7 +2030,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2049,7 +2047,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2066,7 +2064,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2083,7 +2081,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2100,7 +2098,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2117,7 +2115,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2134,7 +2132,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2151,7 +2149,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2168,7 +2166,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2185,7 +2183,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2202,7 +2200,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2219,7 +2217,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2236,7 +2234,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2251,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2270,7 +2268,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2287,7 +2285,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2304,12 +2302,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2321,7 +2319,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2338,7 +2336,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2355,7 +2353,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2372,7 +2370,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2389,7 +2387,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2406,24 +2404,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2440,7 +2438,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2457,7 +2455,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2474,7 +2472,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2491,7 +2489,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2508,12 +2506,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2525,7 +2523,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2542,7 +2540,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2559,17 +2557,134 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
@@ -438,9 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,9 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -493,9 +487,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -503,18 +494,12 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>BAU compute Business as usual scenario</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -548,31 +533,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -589,8 +574,6 @@
           <t>M inhabitant</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>INSEE data</t>
@@ -608,8 +591,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Logistic</t>
@@ -627,8 +608,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -646,8 +625,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -665,8 +642,6 @@
           <t>kgN/cap/yr</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -684,8 +659,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -703,8 +676,6 @@
           <t>ha</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -714,7 +685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Net import of vegetal pdcts</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -722,68 +693,94 @@
           <t>ktN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend. Used as a goal but may be adjusted according to territory situation</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>ktN</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>LU</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Synth N fertilizer application to cropland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>kgN/ha/yr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>kgN/ha/yr</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1068,6 @@
       <c r="E12" t="n">
         <v>281</v>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1091,7 +1087,6 @@
       <c r="E13" t="n">
         <v>75</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1155,7 +1150,6 @@
       <c r="E16" t="n">
         <v>45</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1175,7 +1169,6 @@
       <c r="E17" t="n">
         <v>60</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1601,7 +1594,6 @@
           <t xml:space="preserve">Natural meadow </t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="b">
         <v>0</v>
       </c>
@@ -1626,31 +1618,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Business as usual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -1662,11 +1654,9 @@
           <t>Weight diet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1679,11 +1669,9 @@
           <t>Weight synthetic fertilizer use</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1693,14 +1681,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weight import/export balance</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Weight import</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Weight for the optimization model</t>
@@ -1710,64 +1696,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1775,8 +1749,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1786,64 +1758,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1851,8 +1817,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1862,7 +1826,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1870,8 +1834,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1881,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1889,8 +1851,6 @@
           <t>kgN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Historical trend</t>
@@ -1900,64 +1860,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>kgN</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1965,8 +1919,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1976,7 +1928,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1984,8 +1936,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -1995,7 +1945,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2003,8 +1953,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2014,7 +1962,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2022,8 +1970,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2033,7 +1979,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2041,8 +1987,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2052,7 +1996,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2060,8 +2004,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2071,7 +2013,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2079,8 +2021,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2090,7 +2030,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2098,8 +2038,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2109,7 +2047,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2117,8 +2055,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2128,7 +2064,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2136,8 +2072,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2147,7 +2081,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2155,8 +2089,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2166,7 +2098,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2174,8 +2106,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2185,7 +2115,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2193,8 +2123,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2204,7 +2132,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2212,8 +2140,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2223,7 +2149,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2231,8 +2157,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2242,7 +2166,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2250,8 +2174,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2261,7 +2183,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2269,8 +2191,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2280,7 +2200,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2288,8 +2208,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2299,7 +2217,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2307,8 +2225,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2318,7 +2234,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2326,8 +2242,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2337,7 +2251,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2345,8 +2259,6 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2356,16 +2268,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2375,16 +2285,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2394,16 +2302,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2413,7 +2319,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2421,8 +2327,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2432,7 +2336,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2440,8 +2344,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2451,7 +2353,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2459,8 +2361,6 @@
           <t>prop</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
@@ -2470,64 +2370,58 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+          <t>prop</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2535,8 +2429,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2546,7 +2438,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2554,8 +2446,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2565,7 +2455,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2573,8 +2463,6 @@
           <t>kgcarcass/LU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2584,16 +2472,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2603,16 +2489,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2622,16 +2506,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+          <t>kgcarcass/LU</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
@@ -2641,19 +2523,168 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Bovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,24 +583,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Urban population</t>
+          <t>Total per capita protein ingestion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN/cap/yr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total per capita protein ingestion</t>
+          <t>Vegetal per capita protein ingestion</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vegetal per capita protein ingestion</t>
+          <t>Edible animal per capita protein ingestion (excl fish)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -634,24 +634,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Edible animal per capita protein ingestion (excl fish)</t>
+          <t>Arable area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kgN/cap/yr</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arable area</t>
+          <t>Permanent grassland area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -668,24 +668,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Permanent grassland area</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>ktN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Import of vegetal pdcts</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -702,41 +702,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Export of vegetal pdcts</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ktN</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Synth N fertilizer application to cropland</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>kgN/ha/yr</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,32 +753,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to grassland</t>
+          <t>Methaniser production</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
+          <t>GWh/yr</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methaniser production</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh/yr</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
@@ -1618,7 +1601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,6 +1630,11 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1662,6 +1650,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1677,6 +1668,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1692,6 +1686,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1707,6 +1704,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1722,6 +1722,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1737,28 +1740,31 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+          <t>Urban population</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Logistic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1770,12 +1776,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1787,12 +1796,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1804,29 +1816,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Historical trend</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1838,12 +1856,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1855,12 +1876,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1872,12 +1896,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1889,12 +1916,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1906,29 +1936,35 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
-        </is>
+          <t>Historical trend</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1940,12 +1976,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1957,12 +1996,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1974,12 +2016,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1991,12 +2036,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2008,12 +2056,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2025,12 +2076,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2042,12 +2096,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2059,12 +2116,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2076,12 +2136,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2093,12 +2156,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2110,12 +2176,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2127,12 +2196,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2144,12 +2216,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2161,12 +2236,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2178,12 +2256,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2195,12 +2276,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2212,12 +2296,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2229,12 +2316,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2246,12 +2336,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2263,12 +2356,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2280,12 +2376,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F39" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2297,12 +2396,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2314,29 +2416,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F42" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2348,12 +2456,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F43" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2365,12 +2476,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F44" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2382,12 +2496,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F45" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2399,12 +2516,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F46" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2416,29 +2536,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2450,12 +2576,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,12 +2596,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2484,12 +2616,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2501,12 +2636,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F52" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2518,29 +2656,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2552,12 +2696,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2569,12 +2716,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F56" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Poultry dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2586,32 +2736,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F57" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Share of crop residues in methaniser</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.06</v>
+          <t>kg/LU</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Adapted from ONRB data</t>
-        </is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Share of green waste in methaniser</t>
+          <t>Share of crop residues in methaniser</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2620,18 +2773,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Share of dedicated culture in methaniser</t>
+          <t>Share of green waste in methaniser</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2640,18 +2796,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Share of animal food industry in methaniser</t>
+          <t>Share of dedicated culture in methaniser</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2660,32 +2819,61 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Share of livestock effluent in methaniser</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>prop</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>0.79</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F63" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
+++ b/src/grafs_e/data/scenario_region/Exponential/Pyrénées Orient.xlsx
@@ -778,38 +778,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Crops</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Area proportion (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enforce Area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ymax (kgN/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>k (kgN/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>r2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Straw to Grain Ratio</t>
         </is>
       </c>
     </row>
@@ -834,6 +839,9 @@
       <c r="F2" t="n">
         <v>0.36</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.163</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -856,6 +864,9 @@
       <c r="F3" t="n">
         <v>0.11</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -878,6 +889,9 @@
       <c r="F4" t="n">
         <v>0.11</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.167</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -900,11 +914,14 @@
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grain maize</t>
+          <t>Maize</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -922,6 +939,9 @@
       <c r="F6" t="n">
         <v>0.43</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.171</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -944,6 +964,9 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -966,11 +989,14 @@
       <c r="F8" t="n">
         <v>0.25</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.174</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Straw</t>
+          <t>Rapeseed</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -980,145 +1006,163 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>0.33</v>
+        <v>-0.29</v>
+      </c>
+      <c r="G9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rapeseed</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.383666287704592</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.29</v>
+        <v>0.27</v>
+      </c>
+      <c r="G10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.383666287704592</v>
+        <v>0</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>216</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.27</v>
+        <v>281</v>
+      </c>
+      <c r="G11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Other oil crops</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.1278887625681973</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>62</v>
       </c>
       <c r="E12" t="n">
-        <v>281</v>
+        <v>75</v>
+      </c>
+      <c r="G12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Other oil crops</t>
+          <t>Horse beans and faba beans</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1278887625681973</v>
+        <v>0.05115550502727893</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>363</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>569</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Horse beans and faba beans</t>
+          <t>Peas</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05115550502727893</v>
+        <v>1.91833143852296</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>363</v>
+        <v>323</v>
       </c>
       <c r="E14" t="n">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="F14" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
+      </c>
+      <c r="G14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peas</t>
+          <t>Other protein crops</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.91833143852296</v>
+        <v>0</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>323</v>
+        <v>51</v>
       </c>
       <c r="E15" t="n">
-        <v>556</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.84</v>
+        <v>45</v>
+      </c>
+      <c r="G15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other protein crops</t>
+          <t>Sugar beet</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1128,57 +1172,69 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>60</v>
+      </c>
+      <c r="G16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sugar beet</t>
+          <t>Potatoes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>4.476106689886906</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potatoes</t>
+          <t>Other roots</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.476106689886906</v>
+        <v>0</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other roots</t>
+          <t>Green peas</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1188,19 +1244,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.85</v>
+      </c>
+      <c r="G19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Green peas</t>
+          <t>Dry beans</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1210,19 +1269,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>239</v>
       </c>
       <c r="E20" t="n">
-        <v>160</v>
+        <v>427</v>
       </c>
       <c r="F20" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
+      </c>
+      <c r="G20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dry beans</t>
+          <t>Green beans</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1232,19 +1294,22 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="E21" t="n">
-        <v>427</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>0.92</v>
+        <v>0.44</v>
+      </c>
+      <c r="G21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green beans</t>
+          <t>Dry vegetables</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1254,19 +1319,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="F22" t="n">
-        <v>0.44</v>
+        <v>0.85</v>
+      </c>
+      <c r="G22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dry vegetables</t>
+          <t>Dry fruits</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1276,19 +1344,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="E23" t="n">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="F23" t="n">
-        <v>0.85</v>
+        <v>0.27</v>
+      </c>
+      <c r="G23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dry fruits</t>
+          <t>Squash and melons</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1298,19 +1369,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>56</v>
       </c>
       <c r="F24" t="n">
-        <v>0.27</v>
+        <v>0.06</v>
+      </c>
+      <c r="G24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Squash and melons</t>
+          <t>Cabbage</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1320,19 +1394,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="E25" t="n">
-        <v>56</v>
+        <v>442</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06</v>
+        <v>0.65</v>
+      </c>
+      <c r="G25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabbage</t>
+          <t>Leaves vegetables</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1342,19 +1419,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>159</v>
+        <v>37</v>
       </c>
       <c r="E26" t="n">
-        <v>442</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
-        <v>0.65</v>
+        <v>0.09</v>
+      </c>
+      <c r="G26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Leaves vegetables</t>
+          <t>Fruits</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1364,63 +1444,72 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>324</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
+      </c>
+      <c r="G27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Olives</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>11.25421110600136</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>173</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>324</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>0.28</v>
+        <v>-0.3</v>
+      </c>
+      <c r="G28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Citrus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>11.25421110600136</v>
+        <v>0</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3</v>
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Citrus</t>
+          <t>Hemp</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1430,19 +1519,22 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="G30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hemp</t>
+          <t>Flax</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1452,142 +1544,138 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
+      </c>
+      <c r="G31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flax</t>
+          <t>Forage maize</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>11.91923267135599</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>413</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>645</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
+      </c>
+      <c r="G32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forage maize</t>
+          <t>Forage cabbages</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11.91923267135599</v>
+        <v>0.3234984543470076</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>413</v>
+        <v>71</v>
       </c>
       <c r="E33" t="n">
-        <v>645</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forage cabbages</t>
+          <t>Alfalfa and clover</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3234984543470076</v>
+        <v>12.78887625681973</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>71</v>
+        <v>420</v>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>661</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
+      </c>
+      <c r="G34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alfalfa and clover</t>
+          <t>Non-legume temporary meadow</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12.78887625681973</v>
+        <v>16.36976160872926</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>420</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>661</v>
+        <v>26</v>
       </c>
       <c r="F35" t="n">
-        <v>0.66</v>
+        <v>0.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Non-legume temporary meadow</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>16.36976160872926</v>
+          <t xml:space="preserve">Natural meadow </t>
+        </is>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Natural meadow </t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>68</v>
-      </c>
-      <c r="E37" t="n">
-        <v>91</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.08</v>
+      </c>
+      <c r="G36" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1650,9 +1738,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1668,9 +1753,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1686,9 +1768,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1704,9 +1783,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1722,9 +1798,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1740,9 +1813,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1777,9 +1847,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1797,9 +1864,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1817,9 +1881,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1837,9 +1898,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1857,9 +1915,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1877,9 +1932,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1897,9 +1949,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1917,9 +1966,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1937,9 +1983,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1957,9 +2000,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1977,9 +2017,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1997,9 +2034,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2017,9 +2051,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2037,9 +2068,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2057,9 +2085,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2077,9 +2102,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2097,9 +2119,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2117,9 +2136,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2137,9 +2153,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2157,9 +2170,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2177,9 +2187,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2197,9 +2204,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2217,9 +2221,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2237,9 +2238,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2257,9 +2255,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2277,9 +2272,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2297,9 +2289,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2317,9 +2306,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2337,9 +2323,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2357,9 +2340,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2377,9 +2357,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2397,9 +2374,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2417,9 +2391,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2437,9 +2408,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2457,9 +2425,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2477,9 +2442,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2497,9 +2459,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2517,9 +2476,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2537,9 +2493,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2557,9 +2510,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2577,9 +2527,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2597,9 +2544,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2617,9 +2561,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2637,9 +2578,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2657,9 +2595,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2677,9 +2612,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2697,9 +2629,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2717,9 +2646,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2737,9 +2663,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2757,9 +2680,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2780,9 +2700,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2803,9 +2720,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2826,9 +2740,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2849,9 +2760,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2871,9 +2779,6 @@
         <is>
           <t>Adapted from ONRB data</t>
         </is>
-      </c>
-      <c r="F63" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
